--- a/AAII_Financials/Quarterly/HSAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HSAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
   <si>
     <t>HSAI</t>
   </si>
@@ -656,326 +656,339 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>126700</v>
+      </c>
+      <c r="E8" s="3">
         <v>98700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>143000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>111700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>98600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>72400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>98600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>76900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>63100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>49700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>79100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>61100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>60700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>62600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>57700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>46100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>63900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>36100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>30900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>33400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>23100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>24700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>75900</v>
+      </c>
+      <c r="E9" s="3">
         <v>60100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>84400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>64700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>56700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>42200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>60100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>40200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>34700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>30500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>46500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>42400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>42600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>38900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>40400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>29000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>32600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>17200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>15700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E10" s="3">
         <v>38600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>58700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>47000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>41900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>30200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>38500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>36700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>28500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>32600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>18700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>23700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>17300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>17100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>31300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>18900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>15200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>14000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>14800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1001,79 +1014,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E12" s="3">
         <v>29700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>30800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>27800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>25300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>33200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>31400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>27300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>26900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>32200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>22200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>30400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>25200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>22600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>29600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>21800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>17100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>9500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1143,52 +1160,55 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="3">
         <v>-27300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-24300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" s="3">
         <v>-27900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>34</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N14" s="3">
         <v>-1700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>34</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1214,53 +1234,56 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E15" s="3">
         <v>4500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5400</v>
-      </c>
-      <c r="H15" s="3">
-        <v>4500</v>
       </c>
       <c r="I15" s="3">
         <v>4500</v>
       </c>
       <c r="J15" s="3">
+        <v>4500</v>
+      </c>
+      <c r="K15" s="3">
         <v>3100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4200</v>
-      </c>
-      <c r="L15" s="3">
-        <v>3000</v>
       </c>
       <c r="M15" s="3">
         <v>3000</v>
       </c>
       <c r="N15" s="3">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="O15" s="3">
         <v>1800</v>
       </c>
       <c r="P15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q15" s="3">
         <v>2000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1285,8 +1308,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>126400</v>
+      </c>
+      <c r="E17" s="3">
         <v>99900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>155700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>100900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>95400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>77000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>111900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>87900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>76300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>68900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>103800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>84000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>76400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>81200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>77400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>60200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>82800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>36700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>38000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>63100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>25100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>27100</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-11000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-19200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-24700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-22900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-15700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-19700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-14100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-18900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-29700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-15400</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1478,170 +1511,177 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E20" s="3">
         <v>3500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1000</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-3000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>16700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9600</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>-5700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-10100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-16000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-22700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-21400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-11600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-11500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-10000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>700</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="W21" s="3">
         <v>-28600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-11600</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>600</v>
+      </c>
+      <c r="E22" s="3">
         <v>800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>700</v>
-      </c>
-      <c r="I22" s="3">
-        <v>500</v>
       </c>
       <c r="J22" s="3">
         <v>500</v>
@@ -1650,22 +1690,22 @@
         <v>500</v>
       </c>
       <c r="L22" s="3">
+        <v>500</v>
+      </c>
+      <c r="M22" s="3">
         <v>300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>200</v>
-      </c>
-      <c r="O22" s="3">
-        <v>100</v>
       </c>
       <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>34</v>
+      <c r="Q22" s="3">
+        <v>100</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>34</v>
@@ -1676,8 +1716,8 @@
       <c r="T22" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1691,79 +1731,85 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E23" s="3">
         <v>2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>22400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>39800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>20200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-19800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-19400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-19100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-13200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-30400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-12700</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1771,35 +1817,35 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3900</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1819,11 +1865,11 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
@@ -1833,8 +1879,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1904,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E26" s="3">
         <v>2700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>21900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>36000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>20100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-19900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-19400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-19100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-13200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-30300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-12700</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E27" s="3">
         <v>2700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>36000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>20100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-19900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-19400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-19100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-39300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-45500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-308500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-30300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-12700</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2117,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2188,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2259,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2330,150 +2397,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1000</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>3000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E33" s="3">
         <v>2700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>21900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>36000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>20100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-19900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-19400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-19100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-39300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-45500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-308500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-30300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-12700</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2543,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E35" s="3">
         <v>2700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>21900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>36000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>20100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-19900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-19400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-19100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-39300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-45500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-308500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-30300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-12700</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2717,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2744,484 +2830,503 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>222300</v>
+      </c>
+      <c r="E41" s="3">
         <v>179500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>237800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>360100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>381700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>389500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>388900</v>
-      </c>
-      <c r="J41" s="3">
-        <v>308300</v>
       </c>
       <c r="K41" s="3">
         <v>308300</v>
       </c>
       <c r="L41" s="3">
+        <v>308300</v>
+      </c>
+      <c r="M41" s="3">
         <v>216500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>219200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>180300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>284500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>305100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>128800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>103700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>99700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>62000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>130300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>326000</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Y41" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>756600</v>
+      </c>
+      <c r="E42" s="3">
         <v>649300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>443500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>674400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>16900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>51100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>52000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>70000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>174900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>226800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>258700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>163800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>152200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>133300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>182000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>230800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>323500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>223200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>54400</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>181700</v>
+      </c>
+      <c r="E43" s="3">
         <v>169000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>205500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>173100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>160000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>136900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>113800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>126700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>100300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>82500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>80600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>57900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>56300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>53400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>71800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>50900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>31700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>33900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>22900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>17600</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>127900</v>
+      </c>
+      <c r="E44" s="3">
         <v>104600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>95900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>90300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>83700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>67500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>66100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>84300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>92300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>87900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>69900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>68600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>77500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>92400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>91200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>78500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>61300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>52000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>45600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>36600</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Y44" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>54500</v>
+      </c>
+      <c r="E45" s="3">
         <v>50600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>25800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>39500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>23800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>29200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>17900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>34100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>31900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>20800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>20500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>16700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>16900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>11000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>13300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12200</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1345000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1153600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1010700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1337900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>673100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>627800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>641500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>605900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>604400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>594200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>620200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>586500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>598500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>619800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>442000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>430400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>438600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>482400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>435400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>446800</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>66600</v>
+      </c>
+      <c r="E47" s="3">
         <v>223400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>397700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>18400</v>
-      </c>
-      <c r="H47" s="3">
-        <v>4400</v>
       </c>
       <c r="I47" s="3">
         <v>4400</v>
       </c>
       <c r="J47" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K47" s="3">
         <v>4500</v>
-      </c>
-      <c r="K47" s="3">
-        <v>4400</v>
       </c>
       <c r="L47" s="3">
         <v>4400</v>
       </c>
       <c r="M47" s="3">
+        <v>4400</v>
+      </c>
+      <c r="N47" s="3">
         <v>4500</v>
-      </c>
-      <c r="N47" s="3">
-        <v>4400</v>
       </c>
       <c r="O47" s="3">
         <v>4400</v>
       </c>
       <c r="P47" s="3">
+        <v>4400</v>
+      </c>
+      <c r="Q47" s="3">
         <v>4600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4400</v>
-      </c>
-      <c r="S47" s="3">
-        <v>300</v>
       </c>
       <c r="T47" s="3">
         <v>300</v>
@@ -3232,8 +3337,8 @@
       <c r="V47" s="3">
         <v>300</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>34</v>
+      <c r="W47" s="3">
+        <v>300</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>34</v>
@@ -3241,150 +3346,159 @@
       <c r="Y47" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>172800</v>
+        <v>179900</v>
       </c>
       <c r="E48" s="3">
         <v>172800</v>
       </c>
       <c r="F48" s="3">
+        <v>172800</v>
+      </c>
+      <c r="G48" s="3">
         <v>161000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>154500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>146400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>145000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>150700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>141000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>144400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>144300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>102400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>96200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>87600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>77400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>71800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>67200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>44400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>14100</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E49" s="3">
         <v>19100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>19200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>16500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>17600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3300</v>
-      </c>
-      <c r="S49" s="3">
-        <v>3200</v>
       </c>
       <c r="T49" s="3">
         <v>3200</v>
       </c>
       <c r="U49" s="3">
+        <v>3200</v>
+      </c>
+      <c r="V49" s="3">
         <v>2500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8800</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,79 +3642,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E52" s="3">
         <v>11600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>20100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>13900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>12300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>15500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>13900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2300</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,70 +3790,73 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1620000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1580600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1610000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1532900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>874100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>803100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>820600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>792200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>778800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>773700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>798600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>715900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>722400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>741700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>541300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>525500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>521500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>545700</v>
-      </c>
-      <c r="U54" s="3">
-        <v>472300</v>
       </c>
       <c r="V54" s="3">
         <v>472300</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>34</v>
+      <c r="W54" s="3">
+        <v>472300</v>
       </c>
       <c r="X54" s="3" t="s">
         <v>34</v>
@@ -3738,8 +3864,11 @@
       <c r="Y54" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,124 +3922,128 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>110500</v>
+      </c>
+      <c r="E57" s="3">
         <v>86300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>106200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>85300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>81300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>55200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>48700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>40500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>53500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>50200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>39000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>30700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>22800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>24400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>29100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>25100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>17200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9900</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Y57" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E58" s="3">
         <v>69900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>69300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>63000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>69800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>38600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>49500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>31100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>23200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>22400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>20700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>15100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>15200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>16000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>34</v>
       </c>
@@ -3922,210 +4056,219 @@
       <c r="U58" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="W58" s="3">
         <v>1800</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E59" s="3">
         <v>20200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>33800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>29300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>73900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>60900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>57800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>56700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>89100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>55400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>56800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>58000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>105600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>88900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>82200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>112500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>99800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>101400</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>250600</v>
+      </c>
+      <c r="E60" s="3">
         <v>231900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>271000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>232500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>211600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>154700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>223200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>196500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>191100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>178400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>188300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>137700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>131500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>132400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>134700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>113900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>99400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>123200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>112200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>113200</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Y60" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>45700</v>
+      </c>
+      <c r="E61" s="3">
         <v>48600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>52100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>54400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>49000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>51000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>50400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>57400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>61100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>61200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>57200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>33300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>27900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>17100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2600</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4147,79 +4290,85 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6100</v>
+        <v>6000</v>
       </c>
       <c r="E62" s="3">
         <v>6100</v>
       </c>
       <c r="F62" s="3">
+        <v>6100</v>
+      </c>
+      <c r="G62" s="3">
         <v>4200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -4360,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,79 +4586,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>302300</v>
+      </c>
+      <c r="E66" s="3">
         <v>286600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>329200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>291100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>266200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>213600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>281900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>261500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>259700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>247400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>253900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>173500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>162300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>151700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>140700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>118000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>104100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>124600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>115000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>114300</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Y66" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4716,20 +4884,20 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>844000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>827100</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>802600</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>765000</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4742,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,70 +4984,73 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-424700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-428500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-425200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-439200</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-472300</v>
       </c>
       <c r="H72" s="3">
         <v>-472300</v>
       </c>
       <c r="I72" s="3">
+        <v>-472300</v>
+      </c>
+      <c r="J72" s="3">
         <v>-467100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-507000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-479800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-472900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-466400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-434000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-417100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-429500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-399200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-375900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-342200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-302200</v>
-      </c>
-      <c r="U72" s="3">
-        <v>-38300</v>
       </c>
       <c r="V72" s="3">
         <v>-38300</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>34</v>
+      <c r="W72" s="3">
+        <v>-38300</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>34</v>
@@ -4884,8 +5058,11 @@
       <c r="Y72" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,79 +5280,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1317700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1294100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1280800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1241800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>608000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>589400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>538700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>530700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>519200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>526300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>544700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>542400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>560200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>590100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-443400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-419600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-385100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-343900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>357400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>357900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Y76" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E81" s="3">
         <v>2700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>21900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>36000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>20100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-19900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-19400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-19100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-39300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-45500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-308500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-30300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-12700</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,8 +5611,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5442,8 +5641,8 @@
       <c r="K83" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L83" s="3">
-        <v>1900</v>
+      <c r="L83" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="M83" s="3">
         <v>1900</v>
@@ -5451,41 +5650,44 @@
       <c r="N83" s="3">
         <v>1900</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>34</v>
+      <c r="O83" s="3">
+        <v>1900</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R83" s="3">
         <v>7600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3900</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="W83" s="3">
         <v>1800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,8 +6053,11 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5883,35 +6100,38 @@
       <c r="P89" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R89" s="3">
         <v>-98100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-69900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-40200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-31500</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="W89" s="3">
         <v>-11100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-37000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,8 +6157,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5981,8 +6202,8 @@
       <c r="P91" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -5997,19 +6218,22 @@
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-87800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-24200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,8 +6377,11 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6194,35 +6424,38 @@
       <c r="P94" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R94" s="3">
         <v>157800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>106300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>74900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-273400</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="W94" s="3">
         <v>23900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-44100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>69600</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6292,8 +6526,8 @@
       <c r="P96" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6319,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,8 +6775,11 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6576,35 +6822,38 @@
       <c r="P100" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R100" s="3">
         <v>2100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>331900</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="W100" s="3">
         <v>274800</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>46500</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6632,50 +6881,53 @@
       <c r="K101" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L101" s="3">
-        <v>-1800</v>
+      <c r="L101" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="M101" s="3">
         <v>-1800</v>
       </c>
       <c r="N101" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="O101" s="3">
         <v>2700</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R101" s="3">
         <v>3500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>5100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="V101" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="W101" s="3">
         <v>1800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-700</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-100</v>
       </c>
       <c r="Y101" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6719,30 +6971,33 @@
         <v>0</v>
       </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>65400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>41600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>37200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>26600</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="W102" s="3">
         <v>289500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-34700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>56900</v>
       </c>
     </row>
